--- a/forms/trg/Formulir_TRG_feedtech.xlsx
+++ b/forms/trg/Formulir_TRG_feedtech.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
